--- a/DvorsakNusa/opravljenoDelo/DvorsakNusa.xlsx
+++ b/DvorsakNusa/opravljenoDelo/DvorsakNusa.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nusad\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nusad\Desktop\Alma Mater\GIT\dvorsak_nusa\DvorsakNusa\opravljenoDelo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{380AF2F3-5DF4-4459-ADAF-55FE933CD3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{378988C9-B7B2-4AA8-8029-D5E38113C8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -643,7 +643,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -653,9 +653,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -675,9 +672,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -721,6 +715,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1004,17 +1001,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:N31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" customWidth="1"/>
-    <col min="6" max="6" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="17" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="17" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1">
         <v>1</v>
       </c>
@@ -1052,7 +1049,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>0</v>
       </c>
@@ -1090,7 +1087,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,7 +1122,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>14</v>
       </c>
@@ -1148,7 +1145,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>4</v>
       </c>
@@ -1168,7 +1165,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>5</v>
       </c>
@@ -1188,7 +1185,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>6</v>
       </c>
@@ -1202,7 +1199,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>3</v>
       </c>
@@ -1216,7 +1213,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>9</v>
       </c>
@@ -1227,27 +1224,27 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B20" s="1">
         <v>1</v>
       </c>
@@ -1285,7 +1282,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B21" s="1">
         <v>2</v>
       </c>
@@ -1314,7 +1311,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B22" s="1">
         <v>2</v>
       </c>
@@ -1328,7 +1325,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B23" s="1">
         <v>3</v>
       </c>
@@ -1357,7 +1354,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B24" s="1">
         <v>4</v>
       </c>
@@ -1371,7 +1368,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B25" s="1">
         <v>4</v>
       </c>
@@ -1391,7 +1388,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B26" s="1">
         <v>5</v>
       </c>
@@ -1399,7 +1396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B27" s="1">
         <v>6</v>
       </c>
@@ -1425,7 +1422,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B28" s="1">
         <v>7</v>
       </c>
@@ -1436,7 +1433,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B29" s="1">
         <v>7</v>
       </c>
@@ -1456,7 +1453,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B30" s="1">
         <v>8</v>
       </c>
@@ -1467,7 +1464,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B31" s="1">
         <v>8</v>
       </c>
@@ -1487,106 +1484,106 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E560E397-08D2-4940-85D9-6188CD094F12}">
   <dimension ref="B1:P26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="2" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="3" customWidth="1"/>
-    <col min="4" max="16" width="17.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" style="3" customWidth="1"/>
+    <col min="4" max="16" width="17.5546875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="B2" s="7">
+    <row r="1" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B2" s="6">
         <v>1</v>
       </c>
-      <c r="C2" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="22" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="2:16" ht="225" x14ac:dyDescent="0.25">
-      <c r="B3" s="10"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="5" t="s">
+    <row r="3" spans="2:16" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="B3" s="9"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="P3" s="16" t="s">
+      <c r="P3" s="14" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="2:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="B4" s="8">
+    <row r="4" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B4" s="7">
         <v>1</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="22" t="s">
         <v>47</v>
       </c>
       <c r="F4" s="4"/>
@@ -1598,90 +1595,90 @@
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
-      <c r="P4" s="17" t="s">
+      <c r="P4" s="15" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B5" s="8">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B5" s="7">
         <v>2</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="22" t="s">
         <v>18</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
-      <c r="N5" s="12"/>
-      <c r="P5" s="18" t="s">
+      <c r="N5" s="11"/>
+      <c r="P5" s="16" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="2:16" ht="180" x14ac:dyDescent="0.25">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="5" t="s">
+    <row r="6" spans="2:16" ht="144" x14ac:dyDescent="0.3">
+      <c r="B6" s="7"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4" t="s">
+      <c r="E6" s="22"/>
+      <c r="F6" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="22" t="s">
         <v>62</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
-      <c r="N6" s="12"/>
-    </row>
-    <row r="7" spans="2:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="B7" s="8">
+      <c r="N6" s="11"/>
+    </row>
+    <row r="7" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B7" s="7">
         <v>2</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="19" t="s">
         <v>59</v>
       </c>
       <c r="H7" s="4"/>
@@ -1690,12 +1687,12 @@
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
-      <c r="N7" s="12"/>
-    </row>
-    <row r="8" spans="2:16" ht="285" x14ac:dyDescent="0.25">
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="6" t="s">
+      <c r="N7" s="11"/>
+    </row>
+    <row r="8" spans="2:16" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E8" s="4" t="s">
@@ -1711,77 +1708,77 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
-      <c r="N8" s="12"/>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B9" s="8">
+      <c r="N8" s="11"/>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B9" s="7">
         <v>3</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="C9" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="22" t="s">
         <v>26</v>
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
-      <c r="N9" s="12"/>
-    </row>
-    <row r="10" spans="2:16" ht="120" x14ac:dyDescent="0.25">
-      <c r="B10" s="8"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="6" t="s">
+      <c r="N9" s="11"/>
+    </row>
+    <row r="10" spans="2:16" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="22" t="s">
         <v>75</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
-      <c r="N10" s="12"/>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B11" s="8">
+      <c r="N10" s="11"/>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B11" s="7">
         <v>4</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="C11" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="22" t="s">
         <v>28</v>
       </c>
       <c r="F11" s="4"/>
@@ -1792,15 +1789,15 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
-      <c r="N11" s="12"/>
-    </row>
-    <row r="12" spans="2:16" ht="195" x14ac:dyDescent="0.25">
-      <c r="B12" s="8"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="6" t="s">
+      <c r="N11" s="11"/>
+    </row>
+    <row r="12" spans="2:16" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="22" t="s">
         <v>77</v>
       </c>
       <c r="F12" s="4"/>
@@ -1811,25 +1808,25 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
-      <c r="N12" s="12"/>
-    </row>
-    <row r="13" spans="2:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="B13" s="8">
+      <c r="N12" s="11"/>
+    </row>
+    <row r="13" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="7">
         <v>4</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F13" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="24" t="s">
+      <c r="G13" s="22" t="s">
         <v>30</v>
       </c>
       <c r="H13" s="4"/>
@@ -1838,17 +1835,17 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
-      <c r="N13" s="12"/>
-    </row>
-    <row r="14" spans="2:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="B14" s="8"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="6" t="s">
+      <c r="N13" s="11"/>
+    </row>
+    <row r="14" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4" t="s">
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22" t="s">
         <v>79</v>
       </c>
       <c r="H14" s="4"/>
@@ -1857,25 +1854,25 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
-      <c r="N14" s="12"/>
-    </row>
-    <row r="15" spans="2:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="8">
+      <c r="N14" s="11"/>
+    </row>
+    <row r="15" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B15" s="7">
         <v>5</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6" t="s">
+      <c r="C15" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="22" t="s">
         <v>32</v>
       </c>
       <c r="H15" s="4"/>
@@ -1884,21 +1881,21 @@
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
-      <c r="N15" s="12"/>
-    </row>
-    <row r="16" spans="2:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="B16" s="8"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="6" t="s">
+      <c r="N15" s="11"/>
+    </row>
+    <row r="16" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B16" s="7"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="22" t="s">
         <v>84</v>
       </c>
       <c r="H16" s="4"/>
@@ -1907,19 +1904,19 @@
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
-      <c r="N16" s="12"/>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B17" s="8">
+      <c r="N16" s="11"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B17" s="7">
         <v>5</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D17" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="22" t="s">
         <v>78</v>
       </c>
       <c r="F17" s="4"/>
@@ -1930,12 +1927,12 @@
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
-      <c r="N17" s="12"/>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" s="8"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="6"/>
+      <c r="N17" s="11"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B18" s="7"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="5"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
@@ -1945,28 +1942,28 @@
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
-      <c r="N18" s="12"/>
-    </row>
-    <row r="19" spans="2:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="B19" s="8">
+      <c r="N18" s="11"/>
+    </row>
+    <row r="19" spans="2:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B19" s="7">
         <v>6</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="C19" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="22" t="s">
         <v>93</v>
       </c>
       <c r="I19" s="4"/>
@@ -1974,18 +1971,18 @@
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
-      <c r="N19" s="12"/>
-    </row>
-    <row r="20" spans="2:14" ht="120" x14ac:dyDescent="0.25">
-      <c r="B20" s="8"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="6" t="s">
+      <c r="N19" s="11"/>
+    </row>
+    <row r="20" spans="2:14" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B20" s="7"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="22" t="s">
         <v>89</v>
       </c>
       <c r="G20" s="4"/>
@@ -1995,19 +1992,19 @@
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="12"/>
-    </row>
-    <row r="21" spans="2:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="B21" s="8">
+      <c r="N20" s="11"/>
+    </row>
+    <row r="21" spans="2:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B21" s="7">
         <v>7</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21" s="6" t="s">
+      <c r="C21" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="22" t="s">
         <v>95</v>
       </c>
       <c r="F21" s="4"/>
@@ -2018,12 +2015,12 @@
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
-      <c r="N21" s="12"/>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B22" s="8"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="6" t="s">
+      <c r="N21" s="11"/>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="23" t="s">
         <v>94</v>
       </c>
       <c r="E22" s="4"/>
@@ -2035,28 +2032,28 @@
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="12"/>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B23" s="27">
+      <c r="N22" s="11"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B23" s="25">
         <v>7</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D23" s="25" t="s">
+      <c r="D23" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="F23" s="24" t="s">
+      <c r="F23" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="G23" s="24" t="s">
+      <c r="G23" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="H23" s="24" t="s">
+      <c r="H23" s="22" t="s">
         <v>96</v>
       </c>
       <c r="I23" s="4"/>
@@ -2064,16 +2061,16 @@
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="12"/>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="8">
+      <c r="N23" s="11"/>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B24" s="7">
         <v>8</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D24" s="6" t="s">
+      <c r="C24" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D24" s="23" t="s">
         <v>40</v>
       </c>
       <c r="E24" s="4"/>
@@ -2085,16 +2082,16 @@
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
-      <c r="N24" s="12"/>
-    </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B25" s="11">
+      <c r="N24" s="11"/>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B25" s="10">
         <v>8</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" s="23" t="s">
         <v>40</v>
       </c>
       <c r="E25" s="4"/>
@@ -2106,16 +2103,16 @@
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="12"/>
-    </row>
-    <row r="26" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="14">
+      <c r="N25" s="11"/>
+    </row>
+    <row r="26" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="12">
         <v>9</v>
       </c>
-      <c r="C26" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D26" s="13" t="s">
+      <c r="C26" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="27" t="s">
         <v>40</v>
       </c>
     </row>
